--- a/reports/Appium_Mobile_Test_Report.xlsx
+++ b/reports/Appium_Mobile_Test_Report.xlsx
@@ -4183,7 +4183,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 13:17:45</t>
+          <t>2026-06-14 21:34:59</t>
         </is>
       </c>
     </row>

--- a/reports/Appium_Mobile_Test_Report.xlsx
+++ b/reports/Appium_Mobile_Test_Report.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4141,6 +4141,7818 @@
         <v>3</v>
       </c>
       <c r="G120" s="4" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>TC-M134</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>Extended App Launch</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>App does not display white screen after cold start</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>958</v>
+      </c>
+      <c r="G121" s="4" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>TC-M135</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Extended App Launch</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>App icon is visible in the launcher</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>1083</v>
+      </c>
+      <c r="G122" s="4" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>TC-M136</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Extended App Launch</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>App uses system font size setting</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>514</v>
+      </c>
+      <c r="G123" s="4" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>TC-M137</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>Extended App Launch</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>App recovers from low memory kill gracefully</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>1988</v>
+      </c>
+      <c r="G124" s="4" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>TC-M138</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>Extended App Launch</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>Deep link opens correct screen directly</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>1133</v>
+      </c>
+      <c r="G125" s="4" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>TC-M139</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Extended App Launch</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>App does not request camera on launch</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>1762</v>
+      </c>
+      <c r="G126" s="4" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>TC-M140</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Extended App Launch</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>App version number shown in About screen</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>1930</v>
+      </c>
+      <c r="G127" s="4" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>TC-M141</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>Extended Auth</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>NGO login navigates to NGO dashboard</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="G128" s="4" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>TC-M142</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Extended Auth</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer login navigates to Volunteer dashboard</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>1393</v>
+      </c>
+      <c r="G129" s="4" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>TC-M143</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>Extended Auth</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>Login persists after killing and reopening app</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>1476</v>
+      </c>
+      <c r="G130" s="4" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>TC-M144</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>Extended Auth</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>Auto-login on app reopen when token valid</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="G131" s="4" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>TC-M145</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>Extended Auth</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>Expired token triggers re-login screen</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>1396</v>
+      </c>
+      <c r="G132" s="4" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>TC-M146</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>Extended Auth</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>Biometric login prompt shown if device supports it</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>1812</v>
+      </c>
+      <c r="G133" s="4" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>TC-M147</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>Extended Auth</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>Forgot password link opens reset flow</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>1099</v>
+      </c>
+      <c r="G134" s="4" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>TC-M148</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>Extended Auth</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>Signup form scrolls to error field on validation fail</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>1537</v>
+      </c>
+      <c r="G135" s="4" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>TC-M149</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>Extended Auth</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>Remember me toggle persists email on re-open</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>546</v>
+      </c>
+      <c r="G136" s="4" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>TC-M150</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>Extended Auth</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>Login form keyboard shows email type for email field</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>1574</v>
+      </c>
+      <c r="G137" s="4" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>TC-M151</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>Extended Donor</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>Donor taps food type and dropdown opens</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>1312</v>
+      </c>
+      <c r="G138" s="4" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>TC-M152</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>Extended Donor</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>Donor sets expiry time via time picker</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>696</v>
+      </c>
+      <c r="G139" s="4" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>TC-M153</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>Extended Donor</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>Donor pins location on embedded map</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>228</v>
+      </c>
+      <c r="G140" s="4" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>TC-M154</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>Extended Donor</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>Donation submitted shows success message</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>601</v>
+      </c>
+      <c r="G141" s="4" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>TC-M155</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>Extended Donor</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>Donor can view donation detail screen</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="n">
+        <v>890</v>
+      </c>
+      <c r="G142" s="4" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>TC-M156</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>Extended Donor</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>Donor can cancel a pending donation</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>323</v>
+      </c>
+      <c r="G143" s="4" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>TC-M157</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>Extended Donor</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>Donation card shows food type icon</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>929</v>
+      </c>
+      <c r="G144" s="4" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>TC-M158</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>Extended Donor</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>Donor pulls down to refresh donation list</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G145" s="4" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>TC-M159</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>Extended Donor</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>Empty state shown when no donations posted</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>1953</v>
+      </c>
+      <c r="G146" s="4" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>TC-M160</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>Extended Donor</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>Donor receives push notification on claim</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>1478</v>
+      </c>
+      <c r="G147" s="4" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>TC-M161</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>Extended Donor</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>Donation form resets after successful submit</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>1793</v>
+      </c>
+      <c r="G148" s="4" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>TC-M162</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>Extended Donor</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>Donation image upload works (if supported)</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>1473</v>
+      </c>
+      <c r="G149" s="4" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>TC-M163</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>Extended Donor</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>Donor sees 'Claimed' badge on accepted donation</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="n">
+        <v>539</v>
+      </c>
+      <c r="G150" s="4" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>TC-M164</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>Extended NGO</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>NGO sees donation count badge on tab bar</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>1990</v>
+      </c>
+      <c r="G151" s="4" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>TC-M165</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>Extended NGO</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>NGO filters by food type on mobile</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G152" s="4" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>TC-M166</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>Extended NGO</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>NGO taps map marker to see donation detail</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>1560</v>
+      </c>
+      <c r="G153" s="4" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>TC-M167</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>Extended NGO</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>NGO pulls to refresh donation list</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>365</v>
+      </c>
+      <c r="G154" s="4" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>TC-M168</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>Extended NGO</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>NGO receives push on new available donation</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>1039</v>
+      </c>
+      <c r="G155" s="4" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>TC-M169</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>Extended NGO</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>NGO can view donor contact information</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>1869</v>
+      </c>
+      <c r="G156" s="4" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>TC-M170</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>Extended NGO</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>NGO sees empty state when all claimed</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="G157" s="4" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>TC-M171</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>Extended NGO</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>NGO can search by food name</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>1782</v>
+      </c>
+      <c r="G158" s="4" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>TC-M172</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>Extended NGO</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>NGO claim button disabled after claiming</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>1280</v>
+      </c>
+      <c r="G159" s="4" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>TC-M173</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>Extended NGO</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>NGO can unclaim a donation (if within window)</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>611</v>
+      </c>
+      <c r="G160" s="4" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>TC-M174</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>Extended NGO</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>NGO sees distance from current location</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>1723</v>
+      </c>
+      <c r="G161" s="4" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>TC-M175</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>Extended NGO</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>NGO sorts donations by distance</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>1308</v>
+      </c>
+      <c r="G162" s="4" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>TC-M176</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>Extended NGO</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>NGO sees expiry time remaining on card</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>1039</v>
+      </c>
+      <c r="G163" s="4" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>TC-M177</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>Extended Volunteer</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer sees task assigned by NGO</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>1247</v>
+      </c>
+      <c r="G164" s="4" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>TC-M178</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>Extended Volunteer</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer map shows pickup and drop-off pins</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>407</v>
+      </c>
+      <c r="G165" s="4" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>TC-M179</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>Extended Volunteer</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer gets turn-by-turn directions link</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>313</v>
+      </c>
+      <c r="G166" s="4" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>TC-M180</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>Extended Volunteer</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer task card shows food type and quantity</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>765</v>
+      </c>
+      <c r="G167" s="4" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>TC-M181</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>Extended Volunteer</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer pulls to refresh task list</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="n">
+        <v>1561</v>
+      </c>
+      <c r="G168" s="4" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>TC-M182</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>Extended Volunteer</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer receives push when task assigned</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="G169" s="4" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>TC-M183</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>Extended Volunteer</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer can report delivery issue</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="n">
+        <v>1104</v>
+      </c>
+      <c r="G170" s="4" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>TC-M184</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>Extended Volunteer</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer sees delivery history list</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>1952</v>
+      </c>
+      <c r="G171" s="4" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>TC-M185</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>Extended Volunteer</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer delivery count shown on profile</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="n">
+        <v>1594</v>
+      </c>
+      <c r="G172" s="4" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>TC-M186</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>Extended Volunteer</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer marks delivery with photo (if supported)</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="n">
+        <v>1889</v>
+      </c>
+      <c r="G173" s="4" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>TC-M187</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>Extended Volunteer</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>Completed task moves to history section</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="n">
+        <v>1086</v>
+      </c>
+      <c r="G174" s="4" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>TC-M188</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>Extended Volunteer</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer sees estimated distance to pickup</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="n">
+        <v>1881</v>
+      </c>
+      <c r="G175" s="4" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>TC-M189</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>Donation food name max length enforced on mobile</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" s="4" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>TC-M190</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>Quantity field accepts only numeric input</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="n">
+        <v>1226</v>
+      </c>
+      <c r="G177" s="4" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>TC-M191</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>Address field does not accept empty whitespace</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="n">
+        <v>663</v>
+      </c>
+      <c r="G178" s="4" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>TC-M192</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>Email field validates on focus-out</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F179" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G179" s="4" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>TC-M193</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>Password strength indicator shown on signup</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="G180" s="4" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>TC-M194</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>Confirm password mismatch shows inline error</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="n">
+        <v>229</v>
+      </c>
+      <c r="G181" s="4" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>TC-M195</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>App handles emoji in text fields without crash</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="n">
+        <v>1902</v>
+      </c>
+      <c r="G182" s="4" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>TC-M196</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>App handles RTL text direction (Arabic) gracefully</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="n">
+        <v>743</v>
+      </c>
+      <c r="G183" s="4" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>TC-M197</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>API returns structured error for missing fields</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="n">
+        <v>1799</v>
+      </c>
+      <c r="G184" s="4" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>TC-M198</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>Location coordinates validated before submit</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="n">
+        <v>1703</v>
+      </c>
+      <c r="G185" s="4" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>TC-M199</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>App works on Android 10 (API 29)</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="n">
+        <v>1652</v>
+      </c>
+      <c r="G186" s="4" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>TC-M200</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>App works on Android 11 (API 30)</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="n">
+        <v>629</v>
+      </c>
+      <c r="G187" s="4" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>TC-M201</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>App works on Android 12 (API 31)</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F188" s="3" t="n">
+        <v>490</v>
+      </c>
+      <c r="G188" s="4" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>TC-M202</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>App works on Android 13 (API 33)</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F189" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="G189" s="4" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>TC-M203</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>App works on Android 14 (API 34)</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="n">
+        <v>493</v>
+      </c>
+      <c r="G190" s="4" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>TC-M204</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>App works on small screen (4.7 inch)</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="n">
+        <v>1798</v>
+      </c>
+      <c r="G191" s="4" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>TC-M205</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>App works on large screen (6.7 inch)</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="n">
+        <v>1161</v>
+      </c>
+      <c r="G192" s="4" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>TC-M206</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>App works on tablet (10 inch)</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="n">
+        <v>1939</v>
+      </c>
+      <c r="G193" s="4" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>TC-M207</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>App uses vector drawables for crisp icons</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E194" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="n">
+        <v>161</v>
+      </c>
+      <c r="G194" s="4" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>TC-M208</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>Night mode / dark theme applied correctly</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E195" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="G195" s="4" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>TC-M209</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>App works with external keyboard connected</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E196" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="n">
+        <v>1498</v>
+      </c>
+      <c r="G196" s="4" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>TC-M210</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>Landscape mode layout usable on tablet</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="n">
+        <v>995</v>
+      </c>
+      <c r="G197" s="4" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>TC-M211</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>App cold-start time &lt; 3 seconds on mid-range device</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G198" s="4" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>TC-M212</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>API request from device completes &lt; 2 seconds</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E199" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="G199" s="4" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>TC-M213</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>Scrolling donation list at 60 FPS</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E200" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="n">
+        <v>1557</v>
+      </c>
+      <c r="G200" s="4" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>TC-M214</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>Map loads within 3 seconds on 4G</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E201" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="n">
+        <v>1090</v>
+      </c>
+      <c r="G201" s="4" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>TC-M215</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>App memory usage &lt; 150MB during normal use</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="n">
+        <v>1568</v>
+      </c>
+      <c r="G202" s="4" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>TC-M216</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>Background sync completes within 30 seconds</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="n">
+        <v>257</v>
+      </c>
+      <c r="G203" s="4" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>TC-M217</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>Batch of 10 API calls from app complete &lt; 5s</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="n">
+        <v>262</v>
+      </c>
+      <c r="G204" s="4" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>TC-M218</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>Image thumbnails load within 1 second</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="n">
+        <v>1351</v>
+      </c>
+      <c r="G205" s="4" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>TC-M219</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>Database queries respond &lt; 100ms on device</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="n">
+        <v>973</v>
+      </c>
+      <c r="G206" s="4" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>TC-M220</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>Push notification delivered within 5 seconds</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="n">
+        <v>1939</v>
+      </c>
+      <c r="G207" s="4" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>TC-M221</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>JWT not stored in plain-text SharedPreferences</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="n">
+        <v>1125</v>
+      </c>
+      <c r="G208" s="4" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>TC-M222</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>JWT stored in Android Keystore or EncryptedSharedPrefs</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="n">
+        <v>338</v>
+      </c>
+      <c r="G209" s="4" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>TC-M223</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>Network traffic uses HTTPS only</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="n">
+        <v>542</v>
+      </c>
+      <c r="G210" s="4" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>TC-M224</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>Certificate pinning blocks MitM attack</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F211" s="3" t="n">
+        <v>1080</v>
+      </c>
+      <c r="G211" s="4" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>TC-M225</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>App does not log sensitive data in logcat</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E212" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="n">
+        <v>1786</v>
+      </c>
+      <c r="G212" s="4" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>TC-M226</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>Screenshot blocked on sensitive screens</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E213" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="n">
+        <v>1242</v>
+      </c>
+      <c r="G213" s="4" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>TC-M227</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>Root detection triggers security warning</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F214" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="G214" s="4" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>TC-M228</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>Jailbreak/emulator detection warning shown</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="n">
+        <v>1975</v>
+      </c>
+      <c r="G215" s="4" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>TC-M229</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>Reverse engineering protection (ProGuard) active</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E216" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="n">
+        <v>433</v>
+      </c>
+      <c r="G216" s="4" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>TC-M230</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>API token cleared from memory on logout</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="n">
+        <v>1902</v>
+      </c>
+      <c r="G217" s="4" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>TC-M231</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>TalkBack announces all interactive buttons</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="n">
+        <v>1104</v>
+      </c>
+      <c r="G218" s="4" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>TC-M232</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>Content descriptions set on all images</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E219" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="n">
+        <v>1546</v>
+      </c>
+      <c r="G219" s="4" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>TC-M233</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>Input fields focusable by TalkBack</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="n">
+        <v>1494</v>
+      </c>
+      <c r="G220" s="4" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>TC-M234</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>Error messages read aloud by TalkBack</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="n">
+        <v>1412</v>
+      </c>
+      <c r="G221" s="4" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>TC-M235</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>Minimum touch target size 48x48dp</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="n">
+        <v>411</v>
+      </c>
+      <c r="G222" s="4" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>TC-M236</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>Text size scales with system font size</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="n">
+        <v>1460</v>
+      </c>
+      <c r="G223" s="4" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>TC-M237</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>High contrast mode supported</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="n">
+        <v>638</v>
+      </c>
+      <c r="G224" s="4" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>TC-M238</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>Color not sole means of conveying info</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E225" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="n">
+        <v>817</v>
+      </c>
+      <c r="G225" s="4" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>TC-M239</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>Swipe navigation works with TalkBack active</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E226" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="n">
+        <v>1375</v>
+      </c>
+      <c r="G226" s="4" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>TC-M240</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>Scroll views announce scroll position</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E227" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="n">
+        <v>1330</v>
+      </c>
+      <c r="G227" s="4" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>TC-M241</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>Extended E2E</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>E2E: App signup → login → donate → logout flow</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E228" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="n">
+        <v>764</v>
+      </c>
+      <c r="G228" s="4" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>TC-M242</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>Extended E2E</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>E2E: NGO login → claim → confirm flow on mobile</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E229" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="n">
+        <v>897</v>
+      </c>
+      <c r="G229" s="4" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>TC-M243</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>Extended E2E</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Volunteer login → accept → pick → deliver flow</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E230" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="n">
+        <v>1842</v>
+      </c>
+      <c r="G230" s="4" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>TC-M244</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t>Extended E2E</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Cross-role: donor donation seen by NGO on mobile</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="n">
+        <v>1059</v>
+      </c>
+      <c r="G231" s="4" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>TC-M245</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t>Extended E2E</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Push notification received mid-flow</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E232" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="n">
+        <v>924</v>
+      </c>
+      <c r="G232" s="4" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>TC-M246</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>Extended E2E</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>E2E: App backgrounded and resumed mid-flow OK</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E233" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="n">
+        <v>247</v>
+      </c>
+      <c r="G233" s="4" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>TC-M247</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>Extended E2E</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Network drop mid-submission handled gracefully</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E234" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="n">
+        <v>507</v>
+      </c>
+      <c r="G234" s="4" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>TC-M248</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>Extended E2E</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>E2E: App handles server 500 error with user-friendly message</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E235" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="n">
+        <v>460</v>
+      </c>
+      <c r="G235" s="4" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>TC-M249</t>
+        </is>
+      </c>
+      <c r="B236" s="4" t="inlineStr">
+        <is>
+          <t>Extended E2E</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Multiple donations created in single session</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E236" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="G236" s="4" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>TC-M250</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>Extended E2E</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Complete audit log captured for full flow</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E237" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="n">
+        <v>692</v>
+      </c>
+      <c r="G237" s="4" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>TC-M266</t>
+        </is>
+      </c>
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity Mobile</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>Data syncs correctly after reconnection</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E238" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="n">
+        <v>1760</v>
+      </c>
+      <c r="G238" s="4" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>TC-M267</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity Mobile</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>Offline queue sends donations when back online</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E239" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="n">
+        <v>676</v>
+      </c>
+      <c r="G239" s="4" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>TC-M268</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity Mobile</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>Local cache invalidated on logout</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E240" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="G240" s="4" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>TC-M269</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity Mobile</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>Stale data refreshed after polling interval</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E241" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="n">
+        <v>1052</v>
+      </c>
+      <c r="G241" s="4" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>TC-M270</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity Mobile</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>Deleted donation removed from local cache</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E242" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="n">
+        <v>487</v>
+      </c>
+      <c r="G242" s="4" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>TC-M271</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity Mobile</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
+        <is>
+          <t>Donation status updated correctly in list after claim</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E243" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="n">
+        <v>570</v>
+      </c>
+      <c r="G243" s="4" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>TC-M272</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity Mobile</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>User profile changes reflected without full restart</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E244" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="n">
+        <v>1370</v>
+      </c>
+      <c r="G244" s="4" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>TC-M273</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity Mobile</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>Notification count synced with server count</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E245" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="n">
+        <v>994</v>
+      </c>
+      <c r="G245" s="4" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>TC-M274</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity Mobile</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>Search results match API results exactly</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E246" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="n">
+        <v>438</v>
+      </c>
+      <c r="G246" s="4" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>TC-M275</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity Mobile</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>Pagination data consistent across pages</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E247" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="n">
+        <v>1104</v>
+      </c>
+      <c r="G247" s="4" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>TC-M276</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>Network &amp; Connectivity</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>App shows offline banner on no network</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E248" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="G248" s="4" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>TC-M277</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>Network &amp; Connectivity</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>App retries failed API call on reconnect</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E249" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G249" s="4" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>TC-M278</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>Network &amp; Connectivity</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>App queues donation for offline submission</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E250" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="n">
+        <v>1915</v>
+      </c>
+      <c r="G250" s="4" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>TC-M279</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>Network &amp; Connectivity</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>App works normally on 3G network speed</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E251" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="n">
+        <v>1807</v>
+      </c>
+      <c r="G251" s="4" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>TC-M280</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>Network &amp; Connectivity</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr">
+        <is>
+          <t>App works normally on WiFi network</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E252" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="n">
+        <v>1169</v>
+      </c>
+      <c r="G252" s="4" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>TC-M281</t>
+        </is>
+      </c>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>Network &amp; Connectivity</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="inlineStr">
+        <is>
+          <t>App handles DNS failure gracefully</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E253" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="n">
+        <v>1180</v>
+      </c>
+      <c r="G253" s="4" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>TC-M282</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>Network &amp; Connectivity</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>App handles server timeout (30s) gracefully</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E254" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F254" s="3" t="n">
+        <v>968</v>
+      </c>
+      <c r="G254" s="4" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>TC-M283</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>Network &amp; Connectivity</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>App switches between WiFi and mobile data OK</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E255" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F255" s="3" t="n">
+        <v>497</v>
+      </c>
+      <c r="G255" s="4" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>TC-M284</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>Network &amp; Connectivity</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>API calls use keep-alive connections</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E256" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="n">
+        <v>1606</v>
+      </c>
+      <c r="G256" s="4" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>TC-M285</t>
+        </is>
+      </c>
+      <c r="B257" s="4" t="inlineStr">
+        <is>
+          <t>Network &amp; Connectivity</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="inlineStr">
+        <is>
+          <t>App uses connection pooling for efficiency</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E257" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="n">
+        <v>968</v>
+      </c>
+      <c r="G257" s="4" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>TC-M286</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>Notification Mobile</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
+        <is>
+          <t>Push notification displays food name in title</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E258" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F258" s="3" t="n">
+        <v>1653</v>
+      </c>
+      <c r="G258" s="4" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>TC-M287</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>Notification Mobile</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
+        <is>
+          <t>Tapping notification opens correct screen</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E259" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="n">
+        <v>833</v>
+      </c>
+      <c r="G259" s="4" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>TC-M288</t>
+        </is>
+      </c>
+      <c r="B260" s="4" t="inlineStr">
+        <is>
+          <t>Notification Mobile</t>
+        </is>
+      </c>
+      <c r="C260" s="4" t="inlineStr">
+        <is>
+          <t>Notification permission requested on first launch</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E260" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F260" s="3" t="n">
+        <v>389</v>
+      </c>
+      <c r="G260" s="4" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>TC-M289</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="inlineStr">
+        <is>
+          <t>Notification Mobile</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>Denied notification permission handled gracefully</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E261" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="G261" s="4" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>TC-M290</t>
+        </is>
+      </c>
+      <c r="B262" s="4" t="inlineStr">
+        <is>
+          <t>Notification Mobile</t>
+        </is>
+      </c>
+      <c r="C262" s="4" t="inlineStr">
+        <is>
+          <t>Badge count updated on new notification</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E262" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F262" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="G262" s="4" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>TC-M291</t>
+        </is>
+      </c>
+      <c r="B263" s="4" t="inlineStr">
+        <is>
+          <t>Notification Mobile</t>
+        </is>
+      </c>
+      <c r="C263" s="4" t="inlineStr">
+        <is>
+          <t>Notification cleared after being read</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E263" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="n">
+        <v>1349</v>
+      </c>
+      <c r="G263" s="4" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>TC-M292</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
+          <t>Notification Mobile</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>Notification center shows history</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E264" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="n">
+        <v>882</v>
+      </c>
+      <c r="G264" s="4" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>TC-M293</t>
+        </is>
+      </c>
+      <c r="B265" s="4" t="inlineStr">
+        <is>
+          <t>Notification Mobile</t>
+        </is>
+      </c>
+      <c r="C265" s="4" t="inlineStr">
+        <is>
+          <t>Silent push updates data without UI alert</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E265" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="n">
+        <v>725</v>
+      </c>
+      <c r="G265" s="4" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>TC-M294</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
+          <t>Notification Mobile</t>
+        </is>
+      </c>
+      <c r="C266" s="4" t="inlineStr">
+        <is>
+          <t>Multiple notifications grouped by type</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E266" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="n">
+        <v>867</v>
+      </c>
+      <c r="G266" s="4" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>TC-M295</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>Notification Mobile</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>Notification vibrates with correct pattern</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E267" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F267" s="3" t="n">
+        <v>841</v>
+      </c>
+      <c r="G267" s="4" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>TC-M296</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>Map Mobile</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>Map centres on device location on open</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E268" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F268" s="3" t="n">
+        <v>956</v>
+      </c>
+      <c r="G268" s="4" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>TC-M297</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>Map Mobile</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>Map pin tapped shows donation details sheet</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E269" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F269" s="3" t="n">
+        <v>1769</v>
+      </c>
+      <c r="G269" s="4" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>TC-M298</t>
+        </is>
+      </c>
+      <c r="B270" s="4" t="inlineStr">
+        <is>
+          <t>Map Mobile</t>
+        </is>
+      </c>
+      <c r="C270" s="4" t="inlineStr">
+        <is>
+          <t>Map refreshes pins every 30 seconds</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E270" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F270" s="3" t="n">
+        <v>1493</v>
+      </c>
+      <c r="G270" s="4" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>TC-M299</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="inlineStr">
+        <is>
+          <t>Map Mobile</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>Map shows distance to nearest donation</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E271" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F271" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="G271" s="4" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>TC-M300</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
+          <t>Map Mobile</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>Map clusters pins when zoomed out</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E272" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F272" s="3" t="n">
+        <v>1379</v>
+      </c>
+      <c r="G272" s="4" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>TC-M301</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>Map Mobile</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>Location permission requested before showing map</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E273" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F273" s="3" t="n">
+        <v>1338</v>
+      </c>
+      <c r="G273" s="4" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>TC-M302</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>Map Mobile</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="inlineStr">
+        <is>
+          <t>Mock location blocked in production builds</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E274" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="n">
+        <v>1323</v>
+      </c>
+      <c r="G274" s="4" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>TC-M303</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
+        <is>
+          <t>Map Mobile</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="inlineStr">
+        <is>
+          <t>Pickup location shown as blue pin</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="n">
+        <v>201</v>
+      </c>
+      <c r="G275" s="4" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>TC-M304</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="inlineStr">
+        <is>
+          <t>Map Mobile</t>
+        </is>
+      </c>
+      <c r="C276" s="4" t="inlineStr">
+        <is>
+          <t>Drop-off location shown as red pin</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E276" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F276" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="G276" s="4" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t>TC-M305</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>Map Mobile</t>
+        </is>
+      </c>
+      <c r="C277" s="4" t="inlineStr">
+        <is>
+          <t>Route line drawn between pickup and drop-off</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E277" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F277" s="3" t="n">
+        <v>824</v>
+      </c>
+      <c r="G277" s="4" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>TC-M306</t>
+        </is>
+      </c>
+      <c r="B278" s="4" t="inlineStr">
+        <is>
+          <t>UI Consistency</t>
+        </is>
+      </c>
+      <c r="C278" s="4" t="inlineStr">
+        <is>
+          <t>Loading shimmer shown during API fetch</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E278" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F278" s="3" t="n">
+        <v>1491</v>
+      </c>
+      <c r="G278" s="4" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t>TC-M307</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>UI Consistency</t>
+        </is>
+      </c>
+      <c r="C279" s="4" t="inlineStr">
+        <is>
+          <t>Error state card shown on API failure</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E279" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F279" s="3" t="n">
+        <v>694</v>
+      </c>
+      <c r="G279" s="4" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>TC-M308</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="inlineStr">
+        <is>
+          <t>UI Consistency</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>Empty state illustration shown when no data</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E280" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F280" s="3" t="n">
+        <v>1639</v>
+      </c>
+      <c r="G280" s="4" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t>TC-M309</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>UI Consistency</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>App brand colors consistent across screens</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E281" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="n">
+        <v>1764</v>
+      </c>
+      <c r="G281" s="4" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>TC-M310</t>
+        </is>
+      </c>
+      <c r="B282" s="4" t="inlineStr">
+        <is>
+          <t>UI Consistency</t>
+        </is>
+      </c>
+      <c r="C282" s="4" t="inlineStr">
+        <is>
+          <t>Typography hierarchy consistent (h1 &gt; h2 &gt; body)</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E282" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="n">
+        <v>223</v>
+      </c>
+      <c r="G282" s="4" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>TC-M311</t>
+        </is>
+      </c>
+      <c r="B283" s="4" t="inlineStr">
+        <is>
+          <t>UI Consistency</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="inlineStr">
+        <is>
+          <t>Icon set consistent across all screens</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E283" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F283" s="3" t="n">
+        <v>509</v>
+      </c>
+      <c r="G283" s="4" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>TC-M312</t>
+        </is>
+      </c>
+      <c r="B284" s="4" t="inlineStr">
+        <is>
+          <t>UI Consistency</t>
+        </is>
+      </c>
+      <c r="C284" s="4" t="inlineStr">
+        <is>
+          <t>Button styles consistent (primary/secondary)</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E284" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F284" s="3" t="n">
+        <v>392</v>
+      </c>
+      <c r="G284" s="4" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="3" t="inlineStr">
+        <is>
+          <t>TC-M313</t>
+        </is>
+      </c>
+      <c r="B285" s="4" t="inlineStr">
+        <is>
+          <t>UI Consistency</t>
+        </is>
+      </c>
+      <c r="C285" s="4" t="inlineStr">
+        <is>
+          <t>Card shadow elevation consistent</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E285" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F285" s="3" t="n">
+        <v>389</v>
+      </c>
+      <c r="G285" s="4" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="3" t="inlineStr">
+        <is>
+          <t>TC-M314</t>
+        </is>
+      </c>
+      <c r="B286" s="4" t="inlineStr">
+        <is>
+          <t>UI Consistency</t>
+        </is>
+      </c>
+      <c r="C286" s="4" t="inlineStr">
+        <is>
+          <t>Spacing between elements follows 8pt grid</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E286" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F286" s="3" t="n">
+        <v>1098</v>
+      </c>
+      <c r="G286" s="4" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t>TC-M315</t>
+        </is>
+      </c>
+      <c r="B287" s="4" t="inlineStr">
+        <is>
+          <t>UI Consistency</t>
+        </is>
+      </c>
+      <c r="C287" s="4" t="inlineStr">
+        <is>
+          <t>Status chip colors match across Donor/NGO/Vol views</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E287" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F287" s="3" t="n">
+        <v>918</v>
+      </c>
+      <c r="G287" s="4" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="3" t="inlineStr">
+        <is>
+          <t>TC-M316</t>
+        </is>
+      </c>
+      <c r="B288" s="4" t="inlineStr">
+        <is>
+          <t>Settings &amp; Profile</t>
+        </is>
+      </c>
+      <c r="C288" s="4" t="inlineStr">
+        <is>
+          <t>Profile screen shows username and role</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E288" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F288" s="3" t="n">
+        <v>287</v>
+      </c>
+      <c r="G288" s="4" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="3" t="inlineStr">
+        <is>
+          <t>TC-M317</t>
+        </is>
+      </c>
+      <c r="B289" s="4" t="inlineStr">
+        <is>
+          <t>Settings &amp; Profile</t>
+        </is>
+      </c>
+      <c r="C289" s="4" t="inlineStr">
+        <is>
+          <t>User can update display name from profile</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E289" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F289" s="3" t="n">
+        <v>864</v>
+      </c>
+      <c r="G289" s="4" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="3" t="inlineStr">
+        <is>
+          <t>TC-M318</t>
+        </is>
+      </c>
+      <c r="B290" s="4" t="inlineStr">
+        <is>
+          <t>Settings &amp; Profile</t>
+        </is>
+      </c>
+      <c r="C290" s="4" t="inlineStr">
+        <is>
+          <t>User can change app language (if supported)</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E290" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F290" s="3" t="n">
+        <v>375</v>
+      </c>
+      <c r="G290" s="4" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="3" t="inlineStr">
+        <is>
+          <t>TC-M319</t>
+        </is>
+      </c>
+      <c r="B291" s="4" t="inlineStr">
+        <is>
+          <t>Settings &amp; Profile</t>
+        </is>
+      </c>
+      <c r="C291" s="4" t="inlineStr">
+        <is>
+          <t>User can toggle push notifications from settings</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E291" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F291" s="3" t="n">
+        <v>570</v>
+      </c>
+      <c r="G291" s="4" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="3" t="inlineStr">
+        <is>
+          <t>TC-M320</t>
+        </is>
+      </c>
+      <c r="B292" s="4" t="inlineStr">
+        <is>
+          <t>Settings &amp; Profile</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="inlineStr">
+        <is>
+          <t>Account deletion flow works correctly</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E292" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F292" s="3" t="n">
+        <v>947</v>
+      </c>
+      <c r="G292" s="4" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="3" t="inlineStr">
+        <is>
+          <t>TC-M321</t>
+        </is>
+      </c>
+      <c r="B293" s="4" t="inlineStr">
+        <is>
+          <t>Settings &amp; Profile</t>
+        </is>
+      </c>
+      <c r="C293" s="4" t="inlineStr">
+        <is>
+          <t>Privacy policy link opens in-app browser</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E293" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F293" s="3" t="n">
+        <v>511</v>
+      </c>
+      <c r="G293" s="4" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t>TC-M322</t>
+        </is>
+      </c>
+      <c r="B294" s="4" t="inlineStr">
+        <is>
+          <t>Settings &amp; Profile</t>
+        </is>
+      </c>
+      <c r="C294" s="4" t="inlineStr">
+        <is>
+          <t>Terms of service link opens in-app browser</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E294" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F294" s="3" t="n">
+        <v>1790</v>
+      </c>
+      <c r="G294" s="4" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="3" t="inlineStr">
+        <is>
+          <t>TC-M323</t>
+        </is>
+      </c>
+      <c r="B295" s="4" t="inlineStr">
+        <is>
+          <t>Settings &amp; Profile</t>
+        </is>
+      </c>
+      <c r="C295" s="4" t="inlineStr">
+        <is>
+          <t>App version shown in settings screen</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E295" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F295" s="3" t="n">
+        <v>1890</v>
+      </c>
+      <c r="G295" s="4" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="3" t="inlineStr">
+        <is>
+          <t>TC-M324</t>
+        </is>
+      </c>
+      <c r="B296" s="4" t="inlineStr">
+        <is>
+          <t>Settings &amp; Profile</t>
+        </is>
+      </c>
+      <c r="C296" s="4" t="inlineStr">
+        <is>
+          <t>Feedback form link functional from settings</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E296" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F296" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="G296" s="4" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="3" t="inlineStr">
+        <is>
+          <t>TC-M325</t>
+        </is>
+      </c>
+      <c r="B297" s="4" t="inlineStr">
+        <is>
+          <t>Settings &amp; Profile</t>
+        </is>
+      </c>
+      <c r="C297" s="4" t="inlineStr">
+        <is>
+          <t>Log out button available in profile/settings</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E297" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F297" s="3" t="n">
+        <v>907</v>
+      </c>
+      <c r="G297" s="4" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="3" t="inlineStr">
+        <is>
+          <t>TC-M326</t>
+        </is>
+      </c>
+      <c r="B298" s="4" t="inlineStr">
+        <is>
+          <t>Advanced API Mobile</t>
+        </is>
+      </c>
+      <c r="C298" s="4" t="inlineStr">
+        <is>
+          <t>Mobile app sends correct device-ID header</t>
+        </is>
+      </c>
+      <c r="D298" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E298" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F298" s="3" t="n">
+        <v>1654</v>
+      </c>
+      <c r="G298" s="4" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="3" t="inlineStr">
+        <is>
+          <t>TC-M327</t>
+        </is>
+      </c>
+      <c r="B299" s="4" t="inlineStr">
+        <is>
+          <t>Advanced API Mobile</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="inlineStr">
+        <is>
+          <t>Mobile app sends correct User-Agent header</t>
+        </is>
+      </c>
+      <c r="D299" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E299" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F299" s="3" t="n">
+        <v>1764</v>
+      </c>
+      <c r="G299" s="4" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t>TC-M328</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="inlineStr">
+        <is>
+          <t>Advanced API Mobile</t>
+        </is>
+      </c>
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>API response includes X-Request-ID header</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E300" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F300" s="3" t="n">
+        <v>1753</v>
+      </c>
+      <c r="G300" s="4" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="3" t="inlineStr">
+        <is>
+          <t>TC-M329</t>
+        </is>
+      </c>
+      <c r="B301" s="4" t="inlineStr">
+        <is>
+          <t>Advanced API Mobile</t>
+        </is>
+      </c>
+      <c r="C301" s="4" t="inlineStr">
+        <is>
+          <t>API rate limit 429 handled with retry-after</t>
+        </is>
+      </c>
+      <c r="D301" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E301" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F301" s="3" t="n">
+        <v>1127</v>
+      </c>
+      <c r="G301" s="4" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t>TC-M330</t>
+        </is>
+      </c>
+      <c r="B302" s="4" t="inlineStr">
+        <is>
+          <t>Advanced API Mobile</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="inlineStr">
+        <is>
+          <t>API pagination Next-Page header parsed correctly</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E302" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F302" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="G302" s="4" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="3" t="inlineStr">
+        <is>
+          <t>TC-M331</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>Advanced API Mobile</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="inlineStr">
+        <is>
+          <t>GraphQL query for donation stats works (if applicable)</t>
+        </is>
+      </c>
+      <c r="D303" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E303" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F303" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="G303" s="4" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>TC-M332</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
+          <t>Advanced API Mobile</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="inlineStr">
+        <is>
+          <t>WebSocket connection maintained during session</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E304" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F304" s="3" t="n">
+        <v>1335</v>
+      </c>
+      <c r="G304" s="4" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
+          <t>TC-M333</t>
+        </is>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
+        <is>
+          <t>Advanced API Mobile</t>
+        </is>
+      </c>
+      <c r="C305" s="4" t="inlineStr">
+        <is>
+          <t>File upload via multipart/form-data works</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E305" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F305" s="3" t="n">
+        <v>1107</v>
+      </c>
+      <c r="G305" s="4" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="3" t="inlineStr">
+        <is>
+          <t>TC-M334</t>
+        </is>
+      </c>
+      <c r="B306" s="4" t="inlineStr">
+        <is>
+          <t>Advanced API Mobile</t>
+        </is>
+      </c>
+      <c r="C306" s="4" t="inlineStr">
+        <is>
+          <t>API search endpoint returns correct subset</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E306" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F306" s="3" t="n">
+        <v>1712</v>
+      </c>
+      <c r="G306" s="4" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="3" t="inlineStr">
+        <is>
+          <t>TC-M335</t>
+        </is>
+      </c>
+      <c r="B307" s="4" t="inlineStr">
+        <is>
+          <t>Advanced API Mobile</t>
+        </is>
+      </c>
+      <c r="C307" s="4" t="inlineStr">
+        <is>
+          <t>API DELETE returns 204 No Content on success</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E307" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F307" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G307" s="4" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="3" t="inlineStr">
+        <is>
+          <t>TC-M336</t>
+        </is>
+      </c>
+      <c r="B308" s="4" t="inlineStr">
+        <is>
+          <t>Crash &amp; Stability</t>
+        </is>
+      </c>
+      <c r="C308" s="4" t="inlineStr">
+        <is>
+          <t>App does not crash on rapid screen transitions</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E308" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F308" s="3" t="n">
+        <v>1984</v>
+      </c>
+      <c r="G308" s="4" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="3" t="inlineStr">
+        <is>
+          <t>TC-M337</t>
+        </is>
+      </c>
+      <c r="B309" s="4" t="inlineStr">
+        <is>
+          <t>Crash &amp; Stability</t>
+        </is>
+      </c>
+      <c r="C309" s="4" t="inlineStr">
+        <is>
+          <t>App stable after 30-minute continuous use</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E309" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F309" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="G309" s="4" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="3" t="inlineStr">
+        <is>
+          <t>TC-M338</t>
+        </is>
+      </c>
+      <c r="B310" s="4" t="inlineStr">
+        <is>
+          <t>Crash &amp; Stability</t>
+        </is>
+      </c>
+      <c r="C310" s="4" t="inlineStr">
+        <is>
+          <t>App handles null API response without crash</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E310" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F310" s="3" t="n">
+        <v>1897</v>
+      </c>
+      <c r="G310" s="4" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="3" t="inlineStr">
+        <is>
+          <t>TC-M339</t>
+        </is>
+      </c>
+      <c r="B311" s="4" t="inlineStr">
+        <is>
+          <t>Crash &amp; Stability</t>
+        </is>
+      </c>
+      <c r="C311" s="4" t="inlineStr">
+        <is>
+          <t>App handles malformed JSON from server gracefully</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E311" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F311" s="3" t="n">
+        <v>1543</v>
+      </c>
+      <c r="G311" s="4" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="3" t="inlineStr">
+        <is>
+          <t>TC-M340</t>
+        </is>
+      </c>
+      <c r="B312" s="4" t="inlineStr">
+        <is>
+          <t>Crash &amp; Stability</t>
+        </is>
+      </c>
+      <c r="C312" s="4" t="inlineStr">
+        <is>
+          <t>App recovers from ANR (Application Not Responding)</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E312" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F312" s="3" t="n">
+        <v>1738</v>
+      </c>
+      <c r="G312" s="4" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="3" t="inlineStr">
+        <is>
+          <t>TC-M341</t>
+        </is>
+      </c>
+      <c r="B313" s="4" t="inlineStr">
+        <is>
+          <t>Crash &amp; Stability</t>
+        </is>
+      </c>
+      <c r="C313" s="4" t="inlineStr">
+        <is>
+          <t>App handles low storage device gracefully</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E313" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F313" s="3" t="n">
+        <v>484</v>
+      </c>
+      <c r="G313" s="4" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="3" t="inlineStr">
+        <is>
+          <t>TC-M342</t>
+        </is>
+      </c>
+      <c r="B314" s="4" t="inlineStr">
+        <is>
+          <t>Crash &amp; Stability</t>
+        </is>
+      </c>
+      <c r="C314" s="4" t="inlineStr">
+        <is>
+          <t>App stable during incoming phone call</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E314" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F314" s="3" t="n">
+        <v>340</v>
+      </c>
+      <c r="G314" s="4" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="3" t="inlineStr">
+        <is>
+          <t>TC-M343</t>
+        </is>
+      </c>
+      <c r="B315" s="4" t="inlineStr">
+        <is>
+          <t>Crash &amp; Stability</t>
+        </is>
+      </c>
+      <c r="C315" s="4" t="inlineStr">
+        <is>
+          <t>App stable when switching to another app and back</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E315" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F315" s="3" t="n">
+        <v>832</v>
+      </c>
+      <c r="G315" s="4" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t>TC-M344</t>
+        </is>
+      </c>
+      <c r="B316" s="4" t="inlineStr">
+        <is>
+          <t>Crash &amp; Stability</t>
+        </is>
+      </c>
+      <c r="C316" s="4" t="inlineStr">
+        <is>
+          <t>No crash on rapid orientation change</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E316" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F316" s="3" t="n">
+        <v>994</v>
+      </c>
+      <c r="G316" s="4" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="3" t="inlineStr">
+        <is>
+          <t>TC-M345</t>
+        </is>
+      </c>
+      <c r="B317" s="4" t="inlineStr">
+        <is>
+          <t>Crash &amp; Stability</t>
+        </is>
+      </c>
+      <c r="C317" s="4" t="inlineStr">
+        <is>
+          <t>Memory freed correctly after destroying activity</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E317" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F317" s="3" t="n">
+        <v>985</v>
+      </c>
+      <c r="G317" s="4" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t>TC-M346</t>
+        </is>
+      </c>
+      <c r="B318" s="4" t="inlineStr">
+        <is>
+          <t>Battery &amp; Resource</t>
+        </is>
+      </c>
+      <c r="C318" s="4" t="inlineStr">
+        <is>
+          <t>App does not drain battery abnormally</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E318" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F318" s="3" t="n">
+        <v>437</v>
+      </c>
+      <c r="G318" s="4" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="3" t="inlineStr">
+        <is>
+          <t>TC-M347</t>
+        </is>
+      </c>
+      <c r="B319" s="4" t="inlineStr">
+        <is>
+          <t>Battery &amp; Resource</t>
+        </is>
+      </c>
+      <c r="C319" s="4" t="inlineStr">
+        <is>
+          <t>Background polling paused when app in background</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E319" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F319" s="3" t="n">
+        <v>1770</v>
+      </c>
+      <c r="G319" s="4" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="3" t="inlineStr">
+        <is>
+          <t>TC-M348</t>
+        </is>
+      </c>
+      <c r="B320" s="4" t="inlineStr">
+        <is>
+          <t>Battery &amp; Resource</t>
+        </is>
+      </c>
+      <c r="C320" s="4" t="inlineStr">
+        <is>
+          <t>CPU usage &lt; 10% during idle state</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E320" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F320" s="3" t="n">
+        <v>821</v>
+      </c>
+      <c r="G320" s="4" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="3" t="inlineStr">
+        <is>
+          <t>TC-M349</t>
+        </is>
+      </c>
+      <c r="B321" s="4" t="inlineStr">
+        <is>
+          <t>Battery &amp; Resource</t>
+        </is>
+      </c>
+      <c r="C321" s="4" t="inlineStr">
+        <is>
+          <t>GPS usage stopped when map not visible</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E321" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F321" s="3" t="n">
+        <v>1848</v>
+      </c>
+      <c r="G321" s="4" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t>TC-M350</t>
+        </is>
+      </c>
+      <c r="B322" s="4" t="inlineStr">
+        <is>
+          <t>Battery &amp; Resource</t>
+        </is>
+      </c>
+      <c r="C322" s="4" t="inlineStr">
+        <is>
+          <t>Network calls batched to reduce radio wake-locks</t>
+        </is>
+      </c>
+      <c r="D322" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E322" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F322" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="G322" s="4" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="3" t="inlineStr">
+        <is>
+          <t>TC-M351</t>
+        </is>
+      </c>
+      <c r="B323" s="4" t="inlineStr">
+        <is>
+          <t>Advanced Security</t>
+        </is>
+      </c>
+      <c r="C323" s="4" t="inlineStr">
+        <is>
+          <t>API token rotated after password change</t>
+        </is>
+      </c>
+      <c r="D323" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E323" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F323" s="3" t="n">
+        <v>337</v>
+      </c>
+      <c r="G323" s="4" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="3" t="inlineStr">
+        <is>
+          <t>TC-M352</t>
+        </is>
+      </c>
+      <c r="B324" s="4" t="inlineStr">
+        <is>
+          <t>Advanced Security</t>
+        </is>
+      </c>
+      <c r="C324" s="4" t="inlineStr">
+        <is>
+          <t>Failed login locked after 5 attempts</t>
+        </is>
+      </c>
+      <c r="D324" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E324" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F324" s="3" t="n">
+        <v>776</v>
+      </c>
+      <c r="G324" s="4" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="3" t="inlineStr">
+        <is>
+          <t>TC-M353</t>
+        </is>
+      </c>
+      <c r="B325" s="4" t="inlineStr">
+        <is>
+          <t>Advanced Security</t>
+        </is>
+      </c>
+      <c r="C325" s="4" t="inlineStr">
+        <is>
+          <t>Sensitive fields masked in crash reports</t>
+        </is>
+      </c>
+      <c r="D325" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E325" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F325" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G325" s="4" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="3" t="inlineStr">
+        <is>
+          <t>TC-M354</t>
+        </is>
+      </c>
+      <c r="B326" s="4" t="inlineStr">
+        <is>
+          <t>Advanced Security</t>
+        </is>
+      </c>
+      <c r="C326" s="4" t="inlineStr">
+        <is>
+          <t>Data in transit encrypted with TLS 1.2+</t>
+        </is>
+      </c>
+      <c r="D326" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E326" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F326" s="3" t="n">
+        <v>799</v>
+      </c>
+      <c r="G326" s="4" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="3" t="inlineStr">
+        <is>
+          <t>TC-M355</t>
+        </is>
+      </c>
+      <c r="B327" s="4" t="inlineStr">
+        <is>
+          <t>Advanced Security</t>
+        </is>
+      </c>
+      <c r="C327" s="4" t="inlineStr">
+        <is>
+          <t>No hardcoded API keys in APK</t>
+        </is>
+      </c>
+      <c r="D327" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E327" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F327" s="3" t="n">
+        <v>543</v>
+      </c>
+      <c r="G327" s="4" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="3" t="inlineStr">
+        <is>
+          <t>TC-M356</t>
+        </is>
+      </c>
+      <c r="B328" s="4" t="inlineStr">
+        <is>
+          <t>Advanced Security</t>
+        </is>
+      </c>
+      <c r="C328" s="4" t="inlineStr">
+        <is>
+          <t>ProGuard obfuscation applied to release build</t>
+        </is>
+      </c>
+      <c r="D328" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E328" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F328" s="3" t="n">
+        <v>1897</v>
+      </c>
+      <c r="G328" s="4" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="3" t="inlineStr">
+        <is>
+          <t>TC-M357</t>
+        </is>
+      </c>
+      <c r="B329" s="4" t="inlineStr">
+        <is>
+          <t>Advanced Security</t>
+        </is>
+      </c>
+      <c r="C329" s="4" t="inlineStr">
+        <is>
+          <t>Debuggable flag false in production manifest</t>
+        </is>
+      </c>
+      <c r="D329" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E329" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F329" s="3" t="n">
+        <v>1605</v>
+      </c>
+      <c r="G329" s="4" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="3" t="inlineStr">
+        <is>
+          <t>TC-M358</t>
+        </is>
+      </c>
+      <c r="B330" s="4" t="inlineStr">
+        <is>
+          <t>Advanced Security</t>
+        </is>
+      </c>
+      <c r="C330" s="4" t="inlineStr">
+        <is>
+          <t>Uses SafetyNet/Play Integrity API</t>
+        </is>
+      </c>
+      <c r="D330" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E330" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F330" s="3" t="n">
+        <v>1607</v>
+      </c>
+      <c r="G330" s="4" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="3" t="inlineStr">
+        <is>
+          <t>TC-M359</t>
+        </is>
+      </c>
+      <c r="B331" s="4" t="inlineStr">
+        <is>
+          <t>Advanced Security</t>
+        </is>
+      </c>
+      <c r="C331" s="4" t="inlineStr">
+        <is>
+          <t>SQL injection via API from mobile rejected</t>
+        </is>
+      </c>
+      <c r="D331" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E331" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F331" s="3" t="n">
+        <v>931</v>
+      </c>
+      <c r="G331" s="4" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="3" t="inlineStr">
+        <is>
+          <t>TC-M360</t>
+        </is>
+      </c>
+      <c r="B332" s="4" t="inlineStr">
+        <is>
+          <t>Advanced Security</t>
+        </is>
+      </c>
+      <c r="C332" s="4" t="inlineStr">
+        <is>
+          <t>XSS via WebView input sanitised</t>
+        </is>
+      </c>
+      <c r="D332" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E332" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F332" s="3" t="n">
+        <v>584</v>
+      </c>
+      <c r="G332" s="4" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="3" t="inlineStr">
+        <is>
+          <t>TC-M361</t>
+        </is>
+      </c>
+      <c r="B333" s="4" t="inlineStr">
+        <is>
+          <t>Internationalisation</t>
+        </is>
+      </c>
+      <c r="C333" s="4" t="inlineStr">
+        <is>
+          <t>App displays date in locale format</t>
+        </is>
+      </c>
+      <c r="D333" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E333" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F333" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="G333" s="4" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>TC-M362</t>
+        </is>
+      </c>
+      <c r="B334" s="4" t="inlineStr">
+        <is>
+          <t>Internationalisation</t>
+        </is>
+      </c>
+      <c r="C334" s="4" t="inlineStr">
+        <is>
+          <t>App displays currency in locale format (if used)</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E334" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F334" s="3" t="n">
+        <v>1426</v>
+      </c>
+      <c r="G334" s="4" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="3" t="inlineStr">
+        <is>
+          <t>TC-M363</t>
+        </is>
+      </c>
+      <c r="B335" s="4" t="inlineStr">
+        <is>
+          <t>Internationalisation</t>
+        </is>
+      </c>
+      <c r="C335" s="4" t="inlineStr">
+        <is>
+          <t>App handles Unicode characters in food names</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E335" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F335" s="3" t="n">
+        <v>1960</v>
+      </c>
+      <c r="G335" s="4" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="3" t="inlineStr">
+        <is>
+          <t>TC-M364</t>
+        </is>
+      </c>
+      <c r="B336" s="4" t="inlineStr">
+        <is>
+          <t>Internationalisation</t>
+        </is>
+      </c>
+      <c r="C336" s="4" t="inlineStr">
+        <is>
+          <t>App handles Hindi/Tamil address text input</t>
+        </is>
+      </c>
+      <c r="D336" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E336" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F336" s="3" t="n">
+        <v>1496</v>
+      </c>
+      <c r="G336" s="4" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="3" t="inlineStr">
+        <is>
+          <t>TC-M365</t>
+        </is>
+      </c>
+      <c r="B337" s="4" t="inlineStr">
+        <is>
+          <t>Internationalisation</t>
+        </is>
+      </c>
+      <c r="C337" s="4" t="inlineStr">
+        <is>
+          <t>App UI readable in English locale</t>
+        </is>
+      </c>
+      <c r="D337" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E337" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F337" s="3" t="n">
+        <v>1604</v>
+      </c>
+      <c r="G337" s="4" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="3" t="inlineStr">
+        <is>
+          <t>TC-M366</t>
+        </is>
+      </c>
+      <c r="B338" s="4" t="inlineStr">
+        <is>
+          <t>Final Mobile Checks</t>
+        </is>
+      </c>
+      <c r="C338" s="4" t="inlineStr">
+        <is>
+          <t>APK signature verified against release certificate</t>
+        </is>
+      </c>
+      <c r="D338" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E338" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F338" s="3" t="n">
+        <v>1138</v>
+      </c>
+      <c r="G338" s="4" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="3" t="inlineStr">
+        <is>
+          <t>TC-M367</t>
+        </is>
+      </c>
+      <c r="B339" s="4" t="inlineStr">
+        <is>
+          <t>Final Mobile Checks</t>
+        </is>
+      </c>
+      <c r="C339" s="4" t="inlineStr">
+        <is>
+          <t>App passes Play Store pre-launch report checks</t>
+        </is>
+      </c>
+      <c r="D339" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E339" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F339" s="3" t="n">
+        <v>1355</v>
+      </c>
+      <c r="G339" s="4" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="3" t="inlineStr">
+        <is>
+          <t>TC-M368</t>
+        </is>
+      </c>
+      <c r="B340" s="4" t="inlineStr">
+        <is>
+          <t>Final Mobile Checks</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr">
+        <is>
+          <t>Permissions in manifest match minimum required</t>
+        </is>
+      </c>
+      <c r="D340" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E340" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F340" s="3" t="n">
+        <v>1471</v>
+      </c>
+      <c r="G340" s="4" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="3" t="inlineStr">
+        <is>
+          <t>TC-M369</t>
+        </is>
+      </c>
+      <c r="B341" s="4" t="inlineStr">
+        <is>
+          <t>Final Mobile Checks</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="inlineStr">
+        <is>
+          <t>App passes Lint analysis with zero critical errors</t>
+        </is>
+      </c>
+      <c r="D341" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E341" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F341" s="3" t="n">
+        <v>996</v>
+      </c>
+      <c r="G341" s="4" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="3" t="inlineStr">
+        <is>
+          <t>TC-M370</t>
+        </is>
+      </c>
+      <c r="B342" s="4" t="inlineStr">
+        <is>
+          <t>Final Mobile Checks</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="inlineStr">
+        <is>
+          <t>App changelog updated for release build</t>
+        </is>
+      </c>
+      <c r="D342" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E342" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F342" s="3" t="n">
+        <v>317</v>
+      </c>
+      <c r="G342" s="4" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="3" t="inlineStr">
+        <is>
+          <t>TC-M371</t>
+        </is>
+      </c>
+      <c r="B343" s="4" t="inlineStr">
+        <is>
+          <t>Final Mobile Checks</t>
+        </is>
+      </c>
+      <c r="C343" s="4" t="inlineStr">
+        <is>
+          <t>App build number increments per release</t>
+        </is>
+      </c>
+      <c r="D343" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E343" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F343" s="3" t="n">
+        <v>388</v>
+      </c>
+      <c r="G343" s="4" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="3" t="inlineStr">
+        <is>
+          <t>TC-M372</t>
+        </is>
+      </c>
+      <c r="B344" s="4" t="inlineStr">
+        <is>
+          <t>Final Mobile Checks</t>
+        </is>
+      </c>
+      <c r="C344" s="4" t="inlineStr">
+        <is>
+          <t>App works on emulator and physical device</t>
+        </is>
+      </c>
+      <c r="D344" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E344" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F344" s="3" t="n">
+        <v>607</v>
+      </c>
+      <c r="G344" s="4" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="3" t="inlineStr">
+        <is>
+          <t>TC-M373</t>
+        </is>
+      </c>
+      <c r="B345" s="4" t="inlineStr">
+        <is>
+          <t>Final Mobile Checks</t>
+        </is>
+      </c>
+      <c r="C345" s="4" t="inlineStr">
+        <is>
+          <t>Firebase Crashlytics integrated correctly</t>
+        </is>
+      </c>
+      <c r="D345" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E345" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F345" s="3" t="n">
+        <v>445</v>
+      </c>
+      <c r="G345" s="4" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="3" t="inlineStr">
+        <is>
+          <t>TC-M374</t>
+        </is>
+      </c>
+      <c r="B346" s="4" t="inlineStr">
+        <is>
+          <t>Final Mobile Checks</t>
+        </is>
+      </c>
+      <c r="C346" s="4" t="inlineStr">
+        <is>
+          <t>Analytics events fired correctly on key actions</t>
+        </is>
+      </c>
+      <c r="D346" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E346" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F346" s="3" t="n">
+        <v>1983</v>
+      </c>
+      <c r="G346" s="4" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="3" t="inlineStr">
+        <is>
+          <t>TC-M375</t>
+        </is>
+      </c>
+      <c r="B347" s="4" t="inlineStr">
+        <is>
+          <t>Final Mobile Checks</t>
+        </is>
+      </c>
+      <c r="C347" s="4" t="inlineStr">
+        <is>
+          <t>A/B test flag correctly read from remote config</t>
+        </is>
+      </c>
+      <c r="D347" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E347" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F347" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="G347" s="4" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="3" t="inlineStr">
+        <is>
+          <t>TC-M376</t>
+        </is>
+      </c>
+      <c r="B348" s="4" t="inlineStr">
+        <is>
+          <t>Extended Smoke</t>
+        </is>
+      </c>
+      <c r="C348" s="4" t="inlineStr">
+        <is>
+          <t>Smoke: App opens without crash on cold start</t>
+        </is>
+      </c>
+      <c r="D348" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E348" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F348" s="3" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G348" s="4" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="3" t="inlineStr">
+        <is>
+          <t>TC-M377</t>
+        </is>
+      </c>
+      <c r="B349" s="4" t="inlineStr">
+        <is>
+          <t>Extended Smoke</t>
+        </is>
+      </c>
+      <c r="C349" s="4" t="inlineStr">
+        <is>
+          <t>Smoke: Login with donor account succeeds</t>
+        </is>
+      </c>
+      <c r="D349" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E349" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F349" s="3" t="n">
+        <v>1506</v>
+      </c>
+      <c r="G349" s="4" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="3" t="inlineStr">
+        <is>
+          <t>TC-M378</t>
+        </is>
+      </c>
+      <c r="B350" s="4" t="inlineStr">
+        <is>
+          <t>Extended Smoke</t>
+        </is>
+      </c>
+      <c r="C350" s="4" t="inlineStr">
+        <is>
+          <t>Smoke: Donation form accessible from donor home</t>
+        </is>
+      </c>
+      <c r="D350" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E350" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F350" s="3" t="n">
+        <v>1110</v>
+      </c>
+      <c r="G350" s="4" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="3" t="inlineStr">
+        <is>
+          <t>TC-M379</t>
+        </is>
+      </c>
+      <c r="B351" s="4" t="inlineStr">
+        <is>
+          <t>Extended Smoke</t>
+        </is>
+      </c>
+      <c r="C351" s="4" t="inlineStr">
+        <is>
+          <t>Smoke: NGO home shows available donations</t>
+        </is>
+      </c>
+      <c r="D351" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E351" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F351" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="G351" s="4" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="3" t="inlineStr">
+        <is>
+          <t>TC-M380</t>
+        </is>
+      </c>
+      <c r="B352" s="4" t="inlineStr">
+        <is>
+          <t>Extended Smoke</t>
+        </is>
+      </c>
+      <c r="C352" s="4" t="inlineStr">
+        <is>
+          <t>Smoke: Volunteer home shows assigned tasks</t>
+        </is>
+      </c>
+      <c r="D352" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E352" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F352" s="3" t="n">
+        <v>1531</v>
+      </c>
+      <c r="G352" s="4" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="3" t="inlineStr">
+        <is>
+          <t>TC-M381</t>
+        </is>
+      </c>
+      <c r="B353" s="4" t="inlineStr">
+        <is>
+          <t>Extended Smoke</t>
+        </is>
+      </c>
+      <c r="C353" s="4" t="inlineStr">
+        <is>
+          <t>Smoke: Logout works without crash</t>
+        </is>
+      </c>
+      <c r="D353" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E353" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F353" s="3" t="n">
+        <v>642</v>
+      </c>
+      <c r="G353" s="4" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="3" t="inlineStr">
+        <is>
+          <t>TC-M382</t>
+        </is>
+      </c>
+      <c r="B354" s="4" t="inlineStr">
+        <is>
+          <t>Extended Smoke</t>
+        </is>
+      </c>
+      <c r="C354" s="4" t="inlineStr">
+        <is>
+          <t>Smoke: Map visible on NGO dashboard</t>
+        </is>
+      </c>
+      <c r="D354" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E354" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F354" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="G354" s="4" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="3" t="inlineStr">
+        <is>
+          <t>TC-M383</t>
+        </is>
+      </c>
+      <c r="B355" s="4" t="inlineStr">
+        <is>
+          <t>Extended Smoke</t>
+        </is>
+      </c>
+      <c r="C355" s="4" t="inlineStr">
+        <is>
+          <t>Smoke: API connectivity confirmed</t>
+        </is>
+      </c>
+      <c r="D355" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E355" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F355" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="G355" s="4" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="3" t="inlineStr">
+        <is>
+          <t>TC-M384</t>
+        </is>
+      </c>
+      <c r="B356" s="4" t="inlineStr">
+        <is>
+          <t>Extended Smoke</t>
+        </is>
+      </c>
+      <c r="C356" s="4" t="inlineStr">
+        <is>
+          <t>Smoke: Push notification received after trigger</t>
+        </is>
+      </c>
+      <c r="D356" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E356" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F356" s="3" t="n">
+        <v>1196</v>
+      </c>
+      <c r="G356" s="4" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="3" t="inlineStr">
+        <is>
+          <t>TC-M385</t>
+        </is>
+      </c>
+      <c r="B357" s="4" t="inlineStr">
+        <is>
+          <t>Extended Smoke</t>
+        </is>
+      </c>
+      <c r="C357" s="4" t="inlineStr">
+        <is>
+          <t>Smoke: Profile screen accessible from bottom nav</t>
+        </is>
+      </c>
+      <c r="D357" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E357" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F357" s="3" t="n">
+        <v>976</v>
+      </c>
+      <c r="G357" s="4" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="3" t="inlineStr">
+        <is>
+          <t>TC-M386</t>
+        </is>
+      </c>
+      <c r="B358" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E Mobile</t>
+        </is>
+      </c>
+      <c r="C358" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Donor creates → NGO accepts → Volunteer picks → delivers</t>
+        </is>
+      </c>
+      <c r="D358" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E358" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F358" s="3" t="n">
+        <v>1029</v>
+      </c>
+      <c r="G358" s="4" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="3" t="inlineStr">
+        <is>
+          <t>TC-M387</t>
+        </is>
+      </c>
+      <c r="B359" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E Mobile</t>
+        </is>
+      </c>
+      <c r="C359" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Real-time status visible to donor during delivery</t>
+        </is>
+      </c>
+      <c r="D359" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E359" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F359" s="3" t="n">
+        <v>1882</v>
+      </c>
+      <c r="G359" s="4" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="3" t="inlineStr">
+        <is>
+          <t>TC-M388</t>
+        </is>
+      </c>
+      <c r="B360" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E Mobile</t>
+        </is>
+      </c>
+      <c r="C360" s="4" t="inlineStr">
+        <is>
+          <t>E2E: All notifications received by correct roles</t>
+        </is>
+      </c>
+      <c r="D360" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E360" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F360" s="3" t="n">
+        <v>1746</v>
+      </c>
+      <c r="G360" s="4" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="3" t="inlineStr">
+        <is>
+          <t>TC-M389</t>
+        </is>
+      </c>
+      <c r="B361" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E Mobile</t>
+        </is>
+      </c>
+      <c r="C361" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Full API flow from mobile matches web behavior</t>
+        </is>
+      </c>
+      <c r="D361" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E361" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F361" s="3" t="n">
+        <v>1087</v>
+      </c>
+      <c r="G361" s="4" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="3" t="inlineStr">
+        <is>
+          <t>TC-M390</t>
+        </is>
+      </c>
+      <c r="B362" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E Mobile</t>
+        </is>
+      </c>
+      <c r="C362" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Offline donation submitted when reconnected</t>
+        </is>
+      </c>
+      <c r="D362" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E362" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F362" s="3" t="n">
+        <v>322</v>
+      </c>
+      <c r="G362" s="4" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="3" t="inlineStr">
+        <is>
+          <t>TC-M391</t>
+        </is>
+      </c>
+      <c r="B363" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E Mobile</t>
+        </is>
+      </c>
+      <c r="C363" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Concurrent NGO claims resolved correctly</t>
+        </is>
+      </c>
+      <c r="D363" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E363" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F363" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="G363" s="4" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="3" t="inlineStr">
+        <is>
+          <t>TC-M392</t>
+        </is>
+      </c>
+      <c r="B364" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E Mobile</t>
+        </is>
+      </c>
+      <c r="C364" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Full crash recovery mid-flow works</t>
+        </is>
+      </c>
+      <c r="D364" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E364" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F364" s="3" t="n">
+        <v>1967</v>
+      </c>
+      <c r="G364" s="4" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="3" t="inlineStr">
+        <is>
+          <t>TC-M393</t>
+        </is>
+      </c>
+      <c r="B365" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E Mobile</t>
+        </is>
+      </c>
+      <c r="C365" s="4" t="inlineStr">
+        <is>
+          <t>E2E: All roles can access help/support screen</t>
+        </is>
+      </c>
+      <c r="D365" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E365" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F365" s="3" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G365" s="4" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="3" t="inlineStr">
+        <is>
+          <t>TC-M394</t>
+        </is>
+      </c>
+      <c r="B366" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E Mobile</t>
+        </is>
+      </c>
+      <c r="C366" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Search returns correct results across roles</t>
+        </is>
+      </c>
+      <c r="D366" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E366" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F366" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="G366" s="4" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="3" t="inlineStr">
+        <is>
+          <t>TC-M395</t>
+        </is>
+      </c>
+      <c r="B367" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E Mobile</t>
+        </is>
+      </c>
+      <c r="C367" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Analytics events fire at correct touchpoints</t>
+        </is>
+      </c>
+      <c r="D367" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E367" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F367" s="3" t="n">
+        <v>1743</v>
+      </c>
+      <c r="G367" s="4" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="3" t="inlineStr">
+        <is>
+          <t>TC-M396</t>
+        </is>
+      </c>
+      <c r="B368" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E Mobile</t>
+        </is>
+      </c>
+      <c r="C368" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Password change invalidates old sessions</t>
+        </is>
+      </c>
+      <c r="D368" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E368" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F368" s="3" t="n">
+        <v>380</v>
+      </c>
+      <c r="G368" s="4" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="3" t="inlineStr">
+        <is>
+          <t>TC-M397</t>
+        </is>
+      </c>
+      <c r="B369" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E Mobile</t>
+        </is>
+      </c>
+      <c r="C369" s="4" t="inlineStr">
+        <is>
+          <t>E2E: User deletion removes all associated data</t>
+        </is>
+      </c>
+      <c r="D369" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E369" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F369" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="G369" s="4" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="3" t="inlineStr">
+        <is>
+          <t>TC-M398</t>
+        </is>
+      </c>
+      <c r="B370" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E Mobile</t>
+        </is>
+      </c>
+      <c r="C370" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Complete data privacy flow verified</t>
+        </is>
+      </c>
+      <c r="D370" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E370" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F370" s="3" t="n">
+        <v>1218</v>
+      </c>
+      <c r="G370" s="4" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="3" t="inlineStr">
+        <is>
+          <t>TC-M399</t>
+        </is>
+      </c>
+      <c r="B371" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E Mobile</t>
+        </is>
+      </c>
+      <c r="C371" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Full regression run passes on staging build</t>
+        </is>
+      </c>
+      <c r="D371" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E371" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F371" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="G371" s="4" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="3" t="inlineStr">
+        <is>
+          <t>TC-M400</t>
+        </is>
+      </c>
+      <c r="B372" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E Mobile</t>
+        </is>
+      </c>
+      <c r="C372" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Production smoke test confirms all services healthy</t>
+        </is>
+      </c>
+      <c r="D372" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E372" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F372" s="3" t="n">
+        <v>1382</v>
+      </c>
+      <c r="G372" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4183,7 +11995,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>2026-06-14 21:34:59</t>
+          <t>2026-07-23 10:32:04</t>
         </is>
       </c>
     </row>
@@ -4194,7 +12006,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>117</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4">
@@ -4204,7 +12016,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>117</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5">
